--- a/Excel/EquipQualityConfig.xlsx
+++ b/Excel/EquipQualityConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,14 +27,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
   <si>
     <t>_Id</t>
   </si>
   <si>
-    <t>RandomNum</t>
-  </si>
-  <si>
     <t>AttrIdList</t>
   </si>
   <si>
@@ -69,6 +66,18 @@
   </si>
   <si>
     <t>20,10,10</t>
+  </si>
+  <si>
+    <t>2001,2002,2003</t>
+  </si>
+  <si>
+    <t>5,10,10</t>
+  </si>
+  <si>
+    <t>10,20,20</t>
+  </si>
+  <si>
+    <t>15,30,30</t>
   </si>
 </sst>
 </file>
@@ -1027,16 +1036,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
+  <dimension ref="C3:E14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="16.25" style="1" customWidth="1"/>
-    <col min="5" max="6" width="13.875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="4" max="5" width="13.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:6">
+    <row r="3" ht="13.5" spans="3:5">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1046,13 +1054,10 @@
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+    </row>
+    <row r="4" ht="13.5" spans="3:5">
+      <c r="C4" s="2" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="3:6">
-      <c r="C4" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -1060,94 +1065,103 @@
       <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="3:6">
+    <row r="5" ht="13.5" spans="3:5">
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:4">
+    <row r="6" spans="3:3">
       <c r="C6" s="1">
         <v>1</v>
       </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
     </row>
-    <row r="7" spans="3:4">
+    <row r="7" spans="3:3">
       <c r="C7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="1">
-        <v>2</v>
-      </c>
     </row>
-    <row r="8" spans="3:6">
+    <row r="8" spans="3:5">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="1">
-        <v>3</v>
+      <c r="D8" s="3" t="s">
+        <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="9" spans="3:6">
+    <row r="9" spans="3:5">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="1">
-        <v>4</v>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="10" spans="3:6">
+    <row r="10" spans="3:5">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="1">
-        <v>5</v>
+      <c r="D10" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="11" spans="3:6">
+    <row r="11" spans="3:5">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="1">
-        <v>6</v>
+      <c r="D11" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5">
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>13</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5">
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipQualityConfig.xlsx
+++ b/Excel/EquipQualityConfig.xlsx
@@ -47,22 +47,22 @@
     <t>int[]</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>15,14</t>
-  </si>
-  <si>
-    <t>7,2</t>
-  </si>
-  <si>
-    <t>15,14,16</t>
-  </si>
-  <si>
-    <t>10,5,5</t>
+    <t>1001</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1001,1002</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>1001,1002,1003</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
   </si>
   <si>
     <t>20,10,10</t>
@@ -101,14 +101,14 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="微软雅黑"/>
+      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1037,14 +1037,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C3:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="13.875" style="1" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="11.9166666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.1666666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" ht="13.5" spans="3:5">
+    <row r="3" customHeight="1" spans="3:5">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1055,7 +1057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" ht="13.5" spans="3:5">
+    <row r="4" customHeight="1" spans="3:5">
       <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
@@ -1066,7 +1068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="13.5" spans="3:5">
+    <row r="5" customHeight="1" spans="3:5">
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1077,17 +1079,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="3:3">
+    <row r="6" customHeight="1" spans="3:5">
       <c r="C6" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:3">
+    <row r="7" customHeight="1" spans="3:5">
       <c r="C7" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="3:5">
+    <row r="8" customHeight="1" spans="3:5">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1098,7 +1100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="3:5">
+    <row r="9" customHeight="1" spans="3:5">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1109,7 +1111,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="3:5">
+    <row r="10" customHeight="1" spans="3:5">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1120,7 +1122,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="3:5">
+    <row r="11" customHeight="1" spans="3:5">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1131,7 +1133,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="3:5">
+    <row r="12" customHeight="1" spans="3:5">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1142,7 +1144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="3:5">
+    <row r="13" customHeight="1" spans="3:5">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1153,7 +1155,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="3:5">
+    <row r="14" customHeight="1" spans="3:5">
       <c r="C14" s="1">
         <v>9</v>
       </c>

--- a/Excel/EquipQualityConfig.xlsx
+++ b/Excel/EquipQualityConfig.xlsx
@@ -27,9 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>_Id</t>
+  </si>
+  <si>
+    <t>Level</t>
   </si>
   <si>
     <t>AttrIdList</t>
@@ -1036,17 +1039,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:E14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="4"/>
+  <dimension ref="C3:F14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="11.9166666666667" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.1666666666667" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="3" max="4" width="11.9166666666667" style="1" customWidth="1"/>
+    <col min="5" max="5" width="18.1666666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:5">
+    <row r="3" customHeight="1" spans="3:6">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1056,10 +1059,13 @@
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" customHeight="1" spans="3:5">
+    <row r="4" customHeight="1" spans="3:6">
       <c r="C4" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -1067,108 +1073,141 @@
       <c r="E4" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="3:5">
+    <row r="5" customHeight="1" spans="3:6">
       <c r="C5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="3:5">
+    <row r="6" customHeight="1" spans="3:6">
       <c r="C6" s="1">
         <v>1</v>
       </c>
+      <c r="D6" s="1">
+        <v>60</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="3:5">
+    <row r="7" customHeight="1" spans="3:6">
       <c r="C7" s="1">
         <v>2</v>
       </c>
+      <c r="D7" s="1">
+        <v>60</v>
+      </c>
     </row>
-    <row r="8" customHeight="1" spans="3:5">
+    <row r="8" customHeight="1" spans="3:6">
       <c r="C8" s="1">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>6</v>
+      <c r="D8" s="1">
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="9" customHeight="1" spans="3:5">
+    <row r="9" customHeight="1" spans="3:6">
       <c r="C9" s="1">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="1">
+        <v>60</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" customHeight="1" spans="3:5">
+    <row r="10" customHeight="1" spans="3:6">
       <c r="C10" s="1">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
+      <c r="D10" s="1">
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="F10" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="11" customHeight="1" spans="3:5">
+    <row r="11" customHeight="1" spans="3:6">
       <c r="C11" s="1">
         <v>6</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>10</v>
+      <c r="D11" s="1">
+        <v>60</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:5">
+    <row r="12" customHeight="1" spans="3:6">
       <c r="C12" s="1">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>13</v>
+      <c r="D12" s="1">
+        <v>60</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="F12" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="13" customHeight="1" spans="3:5">
+    <row r="13" customHeight="1" spans="3:6">
       <c r="C13" s="1">
         <v>8</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>13</v>
+      <c r="D13" s="1">
+        <v>60</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:5">
+    <row r="14" customHeight="1" spans="3:6">
       <c r="C14" s="1">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
+      <c r="D14" s="1">
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="D3 D4 D5 C3:C5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
